--- a/labs/lab-10-human-approval-state-machine/data/approval_queue.xlsx
+++ b/labs/lab-10-human-approval-state-machine/data/approval_queue.xlsx
@@ -439,17 +439,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,30 +470,55 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>payload_hash</t>
+          <t>api_path</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>platforms</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>caption</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>decision_hash</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>risk</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>reviewer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>decision_at</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
@@ -502,31 +532,64 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AST-001</t>
+          <t>AST-002</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sha256-demo-001</t>
+          <t>/api/upload_text</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>northstar_training</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Prove campaign contribution</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Read the benchmark</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>419ad8f34f7501f8cfe997939468cc5423dff20c1668584f55c1d830c517ac36</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Aisha</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:30:00+08:00</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Approved for sandbox text post</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -539,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -594,14 +657,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AST-001</t>
+          <t>AST-002</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>payload_hash</t>
+          <t>api_path</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -611,14 +674,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sha256-demo-001</t>
+          <t>/api/upload_text</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>risk</t>
+          <t>user</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -628,14 +691,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>northstar_training</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>reviewer</t>
+          <t>platforms</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -645,14 +708,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aisha</t>
+          <t>linkedin</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>title</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -662,14 +725,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>Prove campaign contribution</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>decision_at</t>
+          <t>caption</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -677,20 +740,113 @@
           <t>Input/output field used by Lab 10</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Read the benchmark</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>decision_hash</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Input/output field used by Lab 10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>419ad8f34f7501f8cfe997939468cc5423dff20c1668584f55c1d830c517ac36</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>risk</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Input/output field used by Lab 10</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>reviewer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Input/output field used by Lab 10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Aisha</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Input/output field used by Lab 10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>decision_at</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Input/output field used by Lab 10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:30:00+08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Input/output field used by Lab 10</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Input/output field used by Lab 10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Approved for sandbox text post</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -726,7 +882,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Acceptance check: Only APPROVED records with a matching payload hash proceed; rejected and changed payloads cannot publish.</t>
+          <t>Acceptance check: Only APPROVED records with a matching SocialPost payload hash proceed; rejected, retargeted or changed payloads cannot publish.</t>
         </is>
       </c>
     </row>
